--- a/JsonConverter/ExcelFiles/Stage.xlsx
+++ b/JsonConverter/ExcelFiles/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAF2B3F-03B3-4491-B02D-4DE7FFAAF7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BA3533-F352-46BC-B605-B79DFC62A15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -80,12 +80,20 @@
     <t>WaveId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>시작 고기 수량</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartMeatCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -140,6 +148,20 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -228,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -261,6 +283,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -486,8 +513,7 @@
   <cols>
     <col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="32.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" style="2" customWidth="1"/>
     <col min="7" max="8" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -503,10 +529,12 @@
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -522,10 +550,12 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -541,10 +571,12 @@
       <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
@@ -560,10 +592,12 @@
       <c r="B4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="18">
+        <v>200</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="8"/>
       <c r="G4" s="1"/>
@@ -583,10 +617,12 @@
       <c r="B5" s="5">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="18">
+        <v>200</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -606,10 +642,12 @@
       <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="18">
+        <v>200</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>

--- a/JsonConverter/ExcelFiles/Stage.xlsx
+++ b/JsonConverter/ExcelFiles/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BA3533-F352-46BC-B605-B79DFC62A15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0106307-DC52-4310-9D17-981CD709642D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -86,6 +86,22 @@
   </si>
   <si>
     <t>StartMeatCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave5_01, wave5_02, wave5_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave4_01, wave4_02, wave4_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -661,10 +677,18 @@
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="1"/>
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>200</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -678,10 +702,18 @@
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="1"/>
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3</v>
+      </c>
+      <c r="C8" s="6">
+        <v>200</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>

--- a/JsonConverter/ExcelFiles/Stage.xlsx
+++ b/JsonConverter/ExcelFiles/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0106307-DC52-4310-9D17-981CD709642D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92E8BCD-8405-42EB-9869-F78E81D3F5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,11 +97,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wave5_01, wave5_02, wave5_03</t>
+    <t>wave4_01, wave4_02, wave4_03, wave4_04, wave4_05</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wave4_01, wave4_02, wave4_03</t>
+    <t>wave5_01, wave5_02, wave5_03, wave5_04, wave5_05, wave5_06, wave5_07, wave5_08</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -529,7 +529,8 @@
   <cols>
     <col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="32.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="88.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" style="2" customWidth="1"/>
     <col min="7" max="8" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -687,7 +688,7 @@
         <v>200</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -712,7 +713,7 @@
         <v>200</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>

--- a/JsonConverter/ExcelFiles/Stage.xlsx
+++ b/JsonConverter/ExcelFiles/Stage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92E8BCD-8405-42EB-9869-F78E81D3F5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755AF109-8C62-4303-BE49-B161403D92EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,18 +65,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wave1_01, wave1_02, wave1_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave2_01, wave2_02, wave2_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave3_01, wave3_02, wave3_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>WaveId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -97,11 +85,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wave4_01, wave4_02, wave4_03, wave4_04, wave4_05</t>
+    <t>wave1_01,wave1_02,wave1_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wave5_01, wave5_02, wave5_03, wave5_04, wave5_05, wave5_06, wave5_07, wave5_08</t>
+    <t>wave2_01,wave2_02,wave2_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave3_01,wave3_02,wave3_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave4_01,wave4_02,wave4_03,wave4_04,wave4_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave5_01,wave5_02,wave5_03,wave5_04,wave5_05,wave5_06,wave5_07,wave5_08</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -547,7 +547,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
@@ -589,10 +589,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
@@ -613,7 +613,7 @@
         <v>200</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="8"/>
@@ -638,7 +638,7 @@
         <v>200</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -663,7 +663,7 @@
         <v>200</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -679,7 +679,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -704,7 +704,7 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5">
         <v>3</v>
